--- a/tests/Metrado.Excel.Tests/Goldens/twelve-of-forty-unclassified.xlsx
+++ b/tests/Metrado.Excel.Tests/Goldens/twelve-of-forty-unclassified.xlsx
@@ -35,6 +35,9 @@
     <x:t>Metrado</x:t>
   </x:si>
   <x:si>
+    <x:t>Unit</x:t>
+  </x:si>
+  <x:si>
     <x:t>Boundary mode</x:t>
   </x:si>
   <x:si>
@@ -42,6 +45,9 @@
   </x:si>
   <x:si>
     <x:t>Floors</x:t>
+  </x:si>
+  <x:si>
+    <x:t>m2</x:t>
   </x:si>
   <x:si>
     <x:t>PARTIDA</x:t>
@@ -563,10 +569,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F35"/>
+  <x:dimension ref="A1:G35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:6">
+    <x:row r="1" spans="1:7">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -574,7 +580,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:6">
+    <x:row r="2" spans="1:7">
       <x:c r="A2" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -593,629 +599,731 @@
       <x:c r="F2" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
+      <x:c r="G2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>293.75</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:6">
+      <x:c r="F3" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
       <x:c r="A4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>293.75</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:6">
+      <x:c r="F4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>23.75</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>26.25</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>27.5</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>28.75</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:7">
       <x:c r="A10" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:7">
       <x:c r="A11" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>31.25</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:7">
       <x:c r="A12" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>32.5</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:7">
       <x:c r="A13" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>33.75</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:7">
       <x:c r="A14" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:7">
       <x:c r="A15" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>213.75</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:6">
+      <x:c r="F15" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:7">
       <x:c r="A16" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>68.75</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="1:6">
+      <x:c r="F16" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:7">
       <x:c r="A17" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:7">
       <x:c r="A18" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:7">
       <x:c r="A19" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>3.75</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:7">
       <x:c r="A20" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:7">
       <x:c r="A21" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>6.25</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:7">
       <x:c r="A22" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>7.5</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:7">
       <x:c r="A23" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>8.75</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:7">
       <x:c r="A24" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:7">
       <x:c r="A25" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>11.25</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:7">
       <x:c r="A26" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>12.5</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:7">
       <x:c r="A27" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>145</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28" spans="1:6">
+      <x:c r="F27" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:7">
       <x:c r="A28" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>13.75</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:7">
       <x:c r="A29" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E29" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:7">
+      <x:c r="A30" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E29" s="0">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:6">
-      <x:c r="A30" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>16.25</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:7">
       <x:c r="A31" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>17.5</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:7">
       <x:c r="A32" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>18.75</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:7">
       <x:c r="A33" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:7">
       <x:c r="A34" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>21.25</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:7">
       <x:c r="A35" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>22.5</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>18</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1237,12 +1345,12 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>12</x:v>
@@ -1253,181 +1361,181 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
         <x:v>54</x:v>
-      </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>62</x:v>
-      </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/tests/Metrado.Excel.Tests/Goldens/twelve-of-forty-unclassified.xlsx
+++ b/tests/Metrado.Excel.Tests/Goldens/twelve-of-forty-unclassified.xlsx
@@ -39,6 +39,12 @@
   </x:si>
   <x:si>
     <x:t>Boundary mode</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Material</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Layers</x:t>
   </x:si>
   <x:si>
     <x:t>CAPITULO</x:t>
@@ -569,10 +575,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G35"/>
+  <x:dimension ref="A1:I35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -580,7 +586,7 @@
         <x:v>28</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:7">
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -602,728 +608,734 @@
       <x:c r="G2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
+      <x:c r="H2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E3" s="0">
         <x:v>293.75</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E4" s="0">
         <x:v>293.75</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="0">
         <x:v>23.75</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
       <x:c r="A6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
       <x:c r="A7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E7" s="0">
         <x:v>26.25</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="0">
         <x:v>27.5</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="0">
         <x:v>28.75</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E10" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="0">
         <x:v>31.25</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="0">
         <x:v>32.5</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E13" s="0">
         <x:v>33.75</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:7">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:9">
+      <x:c r="A15" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G14" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:7">
-      <x:c r="A15" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E15" s="0">
         <x:v>213.75</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:7">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>68.75</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:7">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E17" s="0">
         <x:v>1.25</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E18" s="0">
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E19" s="0">
         <x:v>3.75</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:7">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E20" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>6.25</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E22" s="0">
         <x:v>7.5</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:7">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>8.75</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E24" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E25" s="0">
         <x:v>11.25</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G25" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:7">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E26" s="0">
         <x:v>12.5</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E27" s="0">
         <x:v>145</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:7">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E28" s="0">
         <x:v>13.75</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G28" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E29" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:9">
+      <x:c r="A30" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="E29" s="0">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="F29" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G29" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:7">
-      <x:c r="A30" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B30" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C30" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>16.25</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E31" s="0">
         <x:v>17.5</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E32" s="0">
         <x:v>18.75</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:7">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E33" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G33" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E34" s="0">
         <x:v>21.25</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G34" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:7">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E35" s="0">
         <x:v>22.5</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1340,202 +1352,205 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D15"/>
+  <x:dimension ref="A1:E15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:4">
+    <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:4">
+        <x:v>49</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5">
       <x:c r="A2" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>12</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:4">
+    <x:row r="3" spans="1:5">
       <x:c r="A3" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:4">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
       <x:c r="A4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:4">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
       <x:c r="A5" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:4">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
       <x:c r="A6" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:4">
+    </x:row>
+    <x:row r="7" spans="1:5">
       <x:c r="A7" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:4">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5">
       <x:c r="A8" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:4">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5">
       <x:c r="A9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:4">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5">
       <x:c r="A10" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:4">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:5">
       <x:c r="A11" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="B11" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:4">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:5">
       <x:c r="A12" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B12" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:4">
+    </x:row>
+    <x:row r="13" spans="1:5">
       <x:c r="A13" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:4">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:5">
       <x:c r="A14" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:4">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:5">
       <x:c r="A15" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/tests/Metrado.Excel.Tests/Goldens/twelve-of-forty-unclassified.xlsx
+++ b/tests/Metrado.Excel.Tests/Goldens/twelve-of-forty-unclassified.xlsx
@@ -164,7 +164,7 @@
     <x:t>walls-18</x:t>
   </x:si>
   <x:si>
-    <x:t>Unclassified elements</x:t>
+    <x:t>Unclassified lines</x:t>
   </x:si>
   <x:si>
     <x:t>Count</x:t>
